--- a/louvers/files/reference_xls/price_xls/aerofoil_af150.xlsx
+++ b/louvers/files/reference_xls/price_xls/aerofoil_af150.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A693B05D-7537-0247-991B-4AD2C9FDAB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2882351B-8168-6A46-92FE-34ED0B2EA7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" activeTab="1" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Price" sheetId="4" r:id="rId1"/>
@@ -782,10 +782,10 @@
     <xf numFmtId="1" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1174,39 +1174,39 @@
       </c>
       <c r="B2" s="19">
         <f>C2/10.76391</f>
-        <v>1300.8748679615496</v>
+        <v>1430.9623547577046</v>
       </c>
       <c r="C2" s="20">
         <f>((1000/B8)*'Per m weight'!B4)*A8</f>
-        <v>14002.500000000002</v>
+        <v>15402.750000000002</v>
       </c>
       <c r="D2" s="21">
         <f>+A8*'Per m weight'!B4</f>
-        <v>1400.25</v>
+        <v>1540.2750000000001</v>
       </c>
       <c r="E2" s="28">
         <f>F2/10.76391</f>
-        <v>1414.274418752108</v>
+        <v>1544.3619055482629</v>
       </c>
       <c r="F2" s="29">
         <f>C2+(((('Per m weight'!C4*0.03937)*39.37)*(1000/B8))*'Coating Rate'!C1)</f>
-        <v>15223.122558750001</v>
+        <v>16623.372558750001</v>
       </c>
       <c r="G2" s="30">
         <f>+D2+((('Per m weight'!C3/25.4)*39.37008)*'Coating Rate'!C1)</f>
-        <v>1480.0751622047244</v>
+        <v>1620.1001622047245</v>
       </c>
       <c r="H2" s="37">
         <f>I2/10.76391</f>
-        <v>1573.03378985889</v>
+        <v>1703.121276655045</v>
       </c>
       <c r="I2" s="38">
         <f>C2+(((('Per m weight'!C4*0.03937)*39.37)*(1000/B8))*'Coating Rate'!C2)</f>
-        <v>16931.994141000003</v>
+        <v>18332.244141000003</v>
       </c>
       <c r="J2" s="39">
         <f>+D2+((('Per m weight'!C4/25.4)*39.37008)*'Coating Rate'!C2)</f>
-        <v>1693.2005952755906</v>
+        <v>1833.2255952755906</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1215,39 +1215,39 @@
       </c>
       <c r="B3" s="22">
         <f>C3/10.76391</f>
-        <v>80.755970646354356</v>
+        <v>88.831567710989788</v>
       </c>
       <c r="C3" s="23">
         <f>((((1000/B8)*2)*50/1000)*'Per m weight'!B5)*A8</f>
-        <v>869.25</v>
+        <v>956.17500000000007</v>
       </c>
       <c r="D3" s="24">
         <f>+CEILING(((A8*'Per m weight'!B5)*0.15),10)</f>
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E3" s="31">
         <f>F3/10.76391</f>
-        <v>90.115933568749654</v>
+        <v>98.191530633385099</v>
       </c>
       <c r="F3" s="32">
         <f>C3+(((('Per m weight'!C5*0.03937)*39.37)*((1000/B8)*2)*50/1000)*'Coating Rate'!C1)</f>
-        <v>969.9997985</v>
+        <v>1056.9247985000002</v>
       </c>
       <c r="G3" s="33">
         <f>+D3+((('Per m weight'!C5/25.4)*6)*'Coating Rate'!C1)</f>
-        <v>155.35433070866142</v>
+        <v>165.35433070866142</v>
       </c>
       <c r="H3" s="40">
         <f>I3/10.76391</f>
-        <v>103.21988166010307</v>
+        <v>111.29547872473852</v>
       </c>
       <c r="I3" s="41">
         <f>C3+(((('Per m weight'!C5*0.03937)*39.37)*((1000/B8)*2)*(50/1000))*'Coating Rate'!C2)</f>
-        <v>1111.0495163999999</v>
+        <v>1197.9745164000001</v>
       </c>
       <c r="J3" s="42">
         <f>+D3+((('Per m weight'!C5/25.4)*6)*'Coating Rate'!C2)</f>
-        <v>176.85039370078741</v>
+        <v>186.85039370078741</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B4" s="53">
         <f>C4/10.76391</f>
-        <v>98.87206414769355</v>
+        <v>108.7592705624629</v>
       </c>
       <c r="C4" s="54">
         <f>((((1000/B8)*2)*50/1000)*'Per m weight'!B6)*A8</f>
-        <v>1064.25</v>
+        <v>1170.675</v>
       </c>
       <c r="D4" s="55">
         <f>+CEILING(((A8*'Per m weight'!B6)*0.15),10)</f>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E4" s="47">
         <f>F4/10.76391</f>
-        <v>112.58800981474205</v>
+        <v>122.47521622951139</v>
       </c>
       <c r="F4" s="48">
         <f>C4+(((('Per m weight'!C6*0.03937)*39.37)*((1000/B8)*2)*50/1000)*'Coating Rate'!C1)</f>
-        <v>1211.8872047249999</v>
+        <v>1318.3122047249999</v>
       </c>
       <c r="G4" s="49">
         <f>+D4+((('Per m weight'!C6/25.4)*6)*'Coating Rate'!C1)</f>
-        <v>182.5</v>
+        <v>202.5</v>
       </c>
       <c r="H4" s="59">
         <f>I4/10.76391</f>
-        <v>131.79033374860995</v>
+        <v>141.67754016337929</v>
       </c>
       <c r="I4" s="60">
         <f>C4+(((('Per m weight'!C6*0.03937)*39.37)*((1000/B8)*2)*(50/1000))*'Coating Rate'!C2)</f>
-        <v>1418.5792913400001</v>
+        <v>1525.00429134</v>
       </c>
       <c r="J4" s="61">
         <f>+D4+((('Per m weight'!C6/25.4)*6)*'Coating Rate'!C2)</f>
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1297,29 +1297,29 @@
       </c>
       <c r="B5" s="56">
         <f>SUM(B2:B4)</f>
-        <v>1480.5029027555975</v>
+        <v>1628.5531930311572</v>
       </c>
       <c r="C5" s="57">
         <f>SUM(C2:C4)</f>
-        <v>15936.000000000002</v>
+        <v>17529.600000000002</v>
       </c>
       <c r="D5" s="58"/>
       <c r="E5" s="50">
         <f>SUM(E2:E4)</f>
-        <v>1616.9783621355996</v>
+        <v>1765.0286524111596</v>
       </c>
       <c r="F5" s="51">
         <f>SUM(F2:F4)</f>
-        <v>17405.009561975003</v>
+        <v>18998.609561975001</v>
       </c>
       <c r="G5" s="52"/>
       <c r="H5" s="62">
         <f>SUM(H2:H4)</f>
-        <v>1808.0440052676031</v>
+        <v>1956.0942955431628</v>
       </c>
       <c r="I5" s="63">
         <f>SUM(I2:I4)</f>
-        <v>19461.622948740001</v>
+        <v>21055.222948740004</v>
       </c>
       <c r="J5" s="64"/>
     </row>
@@ -1334,20 +1334,20 @@
     </row>
     <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B8" s="14">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="1"/>
     </row>
   </sheetData>
@@ -1376,11 +1376,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
     </row>
     <row r="2" spans="1:6" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1463,19 +1463,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="65"/>
+      <c r="B1" s="66"/>
       <c r="C1" s="1">
         <v>0.25</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="65"/>
+      <c r="B2" s="66"/>
       <c r="C2" s="1">
         <v>0.6</v>
       </c>
